--- a/Bank File/bin/Debug/Output/Automated Bank File Ingenia bank file october 2025.xlsx
+++ b/Bank File/bin/Debug/Output/Automated Bank File Ingenia bank file october 2025.xlsx
@@ -77,10 +77,10 @@
     <t>IN-ACH-BSP</t>
   </si>
   <si>
-    <t>53501002260225C</t>
-  </si>
-  <si>
-    <t>SALARY OCT2025</t>
+    <t>53501002260306A</t>
+  </si>
+  <si>
+    <t>SALOCT202561216</t>
   </si>
   <si>
     <t>Kirtikumar Patel</t>
@@ -116,7 +116,7 @@
     <t>State Bank of India</t>
   </si>
   <si>
-    <t>53501006260225T</t>
+    <t>53501006260306C</t>
   </si>
   <si>
     <t>Mahavir Hanumant Ghodake</t>
@@ -134,7 +134,7 @@
     <t>Union Bank of India</t>
   </si>
   <si>
-    <t>53501015260225Y</t>
+    <t>53501015260306Z</t>
   </si>
   <si>
     <t>Vivek Chauhan</t>
@@ -149,7 +149,7 @@
     <t>SBIN0008075</t>
   </si>
   <si>
-    <t>53501022260225I</t>
+    <t>53501022260306U</t>
   </si>
   <si>
     <t>Lodha Raviraj Shantilal</t>
@@ -167,7 +167,7 @@
     <t>HDFC Bank</t>
   </si>
   <si>
-    <t>53501024260225C</t>
+    <t>53501024260306N</t>
   </si>
   <si>
     <t>Vivek Dineshkumar Patel</t>
@@ -185,7 +185,7 @@
     <t>ICICI Bank</t>
   </si>
   <si>
-    <t>53501027260225H</t>
+    <t>53501027260306C</t>
   </si>
   <si>
     <t>Deepak Mishra</t>
@@ -200,7 +200,7 @@
     <t>SBIN0010800</t>
   </si>
   <si>
-    <t>53501041260225V</t>
+    <t>53501041260306G</t>
   </si>
   <si>
     <t>Pinkeshbhai Natubhai Lad</t>
@@ -218,7 +218,7 @@
     <t>Axis Bank</t>
   </si>
   <si>
-    <t>53501044260225P</t>
+    <t>53501044260306L</t>
   </si>
   <si>
     <t>Reena Fougat</t>
@@ -233,7 +233,7 @@
     <t>ICIC0000422</t>
   </si>
   <si>
-    <t>53501046260225W</t>
+    <t>53501046260306J</t>
   </si>
   <si>
     <t>Arun Kumar Gupta</t>
@@ -248,7 +248,7 @@
     <t>ICIC0000022</t>
   </si>
   <si>
-    <t>53501048260225D</t>
+    <t>53501048260306W</t>
   </si>
   <si>
     <t>Rajendra Shankar Dive</t>
@@ -260,7 +260,7 @@
     <t>042201511705</t>
   </si>
   <si>
-    <t>53501051260225H</t>
+    <t>53501051260306I</t>
   </si>
   <si>
     <t>Swapnil Mane</t>
@@ -278,7 +278,7 @@
     <t>IDBI Bank</t>
   </si>
   <si>
-    <t>53505001260225U</t>
+    <t>53505001260306H</t>
   </si>
   <si>
     <t>Patel Rajeshbhai Vishnubhai</t>
@@ -296,7 +296,7 @@
     <t>KOTAK Mahindra Bank LTD</t>
   </si>
   <si>
-    <t>53505002260225F</t>
+    <t>53505002260306T</t>
   </si>
   <si>
     <t>Santosh Kushwaha</t>
@@ -308,7 +308,7 @@
     <t>042201539702</t>
   </si>
   <si>
-    <t>53505003260225M</t>
+    <t>53505003260306P</t>
   </si>
   <si>
     <t>Pravinkumar Amarjit Singh</t>
@@ -323,7 +323,7 @@
     <t>SBIN0002671</t>
   </si>
   <si>
-    <t>53505006260225U</t>
+    <t>53505006260306Y</t>
   </si>
   <si>
     <t>Neeraj Kumar</t>
@@ -335,7 +335,7 @@
     <t>042201539196</t>
   </si>
   <si>
-    <t>53505007260225D</t>
+    <t>53505007260306V</t>
   </si>
   <si>
     <t>Suheb Sharafat Dapolkar</t>
@@ -353,7 +353,7 @@
     <t>Bank of India</t>
   </si>
   <si>
-    <t>53505008260225P</t>
+    <t>53505008260306B</t>
   </si>
   <si>
     <t>Chiragbhai Gajubhai Patel</t>
@@ -368,7 +368,7 @@
     <t>SBIN0011007</t>
   </si>
   <si>
-    <t>53505010260225V</t>
+    <t>53505010260306M</t>
   </si>
   <si>
     <t>Rahul Kantilal Padosa</t>
@@ -386,7 +386,7 @@
     <t>The Thane District Central Co-Op Bank Ltd</t>
   </si>
   <si>
-    <t>53505011260225F</t>
+    <t>53505011260306O</t>
   </si>
   <si>
     <t>Lalit Sanjay Jadhav</t>
@@ -401,7 +401,7 @@
     <t>IBKL0001577</t>
   </si>
   <si>
-    <t>53505012260225K</t>
+    <t>53505012260306E</t>
   </si>
   <si>
     <t>Rahul Prakash Bari</t>
@@ -419,7 +419,7 @@
     <t>Bank of Baroda</t>
   </si>
   <si>
-    <t>53505013260225R</t>
+    <t>53505013260306A</t>
   </si>
   <si>
     <t>Krishna Patil</t>
@@ -434,7 +434,7 @@
     <t>HDFC0002260</t>
   </si>
   <si>
-    <t>53505014260225R</t>
+    <t>53505014260306A</t>
   </si>
   <si>
     <t>Sajan Rathod</t>
@@ -452,7 +452,7 @@
     <t>Bank of Maharashtra</t>
   </si>
   <si>
-    <t>53505015260225J</t>
+    <t>53505015260306E</t>
   </si>
   <si>
     <t>Rajesh Kumar</t>
@@ -467,7 +467,7 @@
     <t>Canara Bank</t>
   </si>
   <si>
-    <t>53505016260225U</t>
+    <t>53505016260306I</t>
   </si>
   <si>
     <t>Sonu Kumar</t>
@@ -479,7 +479,7 @@
     <t>HDFC0004705</t>
   </si>
   <si>
-    <t>53505017260225E</t>
+    <t>53505017260306T</t>
   </si>
   <si>
     <t>Arun Yadav</t>
@@ -559,7 +559,7 @@
   <cols>
     <col min="1" max="1" width="21.1315699986049" customWidth="1"/>
     <col min="2" max="2" width="18.0800443376814" customWidth="1"/>
-    <col min="3" max="3" width="17.4271425519671" customWidth="1"/>
+    <col min="3" max="3" width="18.3032575334821" customWidth="1"/>
     <col min="4" max="4" width="25.7204829624721" customWidth="1"/>
     <col min="5" max="5" width="15.1326860700335" customWidth="1"/>
     <col min="6" max="6" width="40.7641906738281" customWidth="1"/>
